--- a/notification.xlsx
+++ b/notification.xlsx
@@ -413,26 +413,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>nom (Base 1)</t>
+          <t>libelle (Table1)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>nom (Base 2)</t>
+          <t>libelle (Table2)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>nom_user (Base 1)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>nom_user (Base 2)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>description (Base 1)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>description (Base 2)</t>
         </is>
@@ -441,84 +451,88 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mr. Jeaneuds</t>
+          <t>meubles de bureau</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mr. Junior</t>
+          <t>meubles de bureau</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mr. Mohamed</t>
+          <t>equipements informatiques</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hélène Rousseau</t>
+          <t>equipements informatiques</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mme. Hermione</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Isabelle Morel</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Développement de l'application mobile</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Maintenance des équipements informatiques</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gestion du projet de refonte du site web</t>
+          <t>Krizostone</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Gestion de la chaîne d'approvisionnement</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Analyse des besoins pour le nouveau système de gestion</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Analyse des données de performance</t>
+          <t>Crizostone</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Devs full</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dev full</t>
         </is>
       </c>
     </row>

--- a/notification.xlsx
+++ b/notification.xlsx
@@ -413,126 +413,72 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>libelle (Table1)</t>
+          <t>lieu (Base 1)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>libelle (Table2)</t>
+          <t>lieu (Base 2)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>nom_user (Base 1)</t>
+          <t>nom_exposition (Base 1)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>nom_user (Base 2)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>description (Base 1)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>description (Base 2)</t>
+          <t>nom_exposition (Base 2)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>meubles de bureau</t>
+          <t>Porto-Novo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>meubles de bureau</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>Abomey</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Produit B</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Produit B DSI</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>equipements informatiques</t>
+          <t>Parakou</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>equipements informatiques</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Krizostone</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Crizostone</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Devs full</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Dev full</t>
+          <t>Parakou</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Produit C</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Produit D</t>
         </is>
       </c>
     </row>

--- a/notification.xlsx
+++ b/notification.xlsx
@@ -1,34 +1,72 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GARBA\Desktop\port_autonome\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="8205"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+  <si>
+    <t>champ</t>
+  </si>
+  <si>
+    <t>v1</t>
+  </si>
+  <si>
+    <t>v2</t>
+  </si>
+  <si>
+    <t>infos</t>
+  </si>
+  <si>
+    <t>garanno</t>
+  </si>
+  <si>
+    <t>rin_itoshi</t>
+  </si>
+  <si>
+    <t>gabimaru</t>
+  </si>
+  <si>
+    <t>hyoma</t>
+  </si>
+  <si>
+    <t>sagiri</t>
+  </si>
+  <si>
+    <t>chigiri</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +85,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,80 +387,55 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>champ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>v2</t>
-        </is>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>infos</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>garanno</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>rin_itoshi</t>
-        </is>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>infos</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>gabimaru</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>hyoma</t>
-        </is>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>infos</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>sagiri</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>chigiri</t>
-        </is>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/notification.xlsx
+++ b/notification.xlsx
@@ -1,72 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GARBA\Desktop\port_autonome\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="8205"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
-  <si>
-    <t>champ</t>
-  </si>
-  <si>
-    <t>v1</t>
-  </si>
-  <si>
-    <t>v2</t>
-  </si>
-  <si>
-    <t>infos</t>
-  </si>
-  <si>
-    <t>garanno</t>
-  </si>
-  <si>
-    <t>rin_itoshi</t>
-  </si>
-  <si>
-    <t>gabimaru</t>
-  </si>
-  <si>
-    <t>hyoma</t>
-  </si>
-  <si>
-    <t>sagiri</t>
-  </si>
-  <si>
-    <t>chigiri</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -85,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -387,55 +408,140 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>statut_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Num_Facture</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>statut_Num_Facture</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Libelle</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>statut_Libelle</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>------</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP001</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>------</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Responsable RH</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>------</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>------</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP002</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>------</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Assistant RH</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>------</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>------</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DRH100</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>------</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Commun DRH</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>------</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/notification.xlsx
+++ b/notification.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,22 +429,22 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Num_Facture</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>statut_Num_Facture</t>
+          <t>statut_nom</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Libelle</t>
+          <t>age</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>statut_Libelle</t>
+          <t>statut_age</t>
         </is>
       </c>
     </row>
@@ -454,31 +454,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>------</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EMP001</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>------</t>
-        </is>
-      </c>
+          <t>Alice</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Responsable RH</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>------</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -486,29 +474,21 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>------</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EMP002</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>------</t>
-        </is>
-      </c>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Assistant RH</t>
+          <t>VIDE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>------</t>
+          <t>VIDE</t>
         </is>
       </c>
     </row>
@@ -518,31 +498,107 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>------</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DRH100</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>------</t>
-        </is>
-      </c>
+          <t>Charlie</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Commun DRH</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>------</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>quarante</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Erreur</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Eve</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Frank</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Erreur</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Grace</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
